--- a/main/ig/FRAttachmentLMCDAFHIR.xlsx
+++ b/main/ig/FRAttachmentLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRAttachmentLMCDAFHIR.xlsx
+++ b/main/ig/FRAttachmentLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRAttachmentLMCDAFHIR.xlsx
+++ b/main/ig/FRAttachmentLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRAttachmentLMCDAFHIR.xlsx
+++ b/main/ig/FRAttachmentLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRAttachmentLMCDAFHIR.xlsx
+++ b/main/ig/FRAttachmentLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRAttachmentLMCDAFHIR.xlsx
+++ b/main/ig/FRAttachmentLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRAttachmentLMCDAFHIR.xlsx
+++ b/main/ig/FRAttachmentLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-attachment</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-attachment|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-document-attache</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-document-attache|0.1.0</t>
   </si>
   <si>
     <t>FRLMAttachment</t>
@@ -145,7 +145,7 @@
     <t>FRLMAttachment.title</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-document-reference-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-document-reference-document|0.1.0</t>
   </si>
   <si>
     <t>FRDocumentReferenceDocument.content.attachment</t>

--- a/main/ig/FRAttachmentLMCDAFHIR.xlsx
+++ b/main/ig/FRAttachmentLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="54">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-attachment|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMAttachment|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -115,31 +115,34 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>Organizer.component:frObservationMedia.observationMedia</t>
+  </si>
+  <si>
     <t>FRCDADocumentAttache.component:frObservationMedia.observationMedia</t>
   </si>
   <si>
     <t>FRLMAttachment.contentType</t>
   </si>
   <si>
-    <t>FRCDADocumentAttache.component:frObservationMedia.observationMedia.value.mediaType</t>
+    <t>Organizer.component:frObservationMedia.observationMedia.value.mediaType</t>
   </si>
   <si>
     <t>FRLMAttachment.language</t>
   </si>
   <si>
-    <t>FRCDADocumentAttache.component:frObservationMedia.observationMedia.languageCode</t>
+    <t>Organizer.component:frObservationMedia.observationMedia.languageCode</t>
   </si>
   <si>
     <t>FRLMAttachment.data</t>
   </si>
   <si>
-    <t>FRCDADocumentAttache.component:frObservationMedia.observationMedia.value</t>
+    <t>Organizer.component:frObservationMedia.observationMedia.value</t>
   </si>
   <si>
     <t>FRLMAttachment.url</t>
   </si>
   <si>
-    <t>FRCDADocumentAttache.component:frObservationMedia.observationMedia.value.reference</t>
+    <t>Organizer.component:frObservationMedia.observationMedia.value.reference</t>
   </si>
   <si>
     <t>FRLMAttachment.title</t>
@@ -148,28 +151,31 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-document-reference-document|0.1.0</t>
   </si>
   <si>
+    <t>DocumentReference.content.attachment</t>
+  </si>
+  <si>
     <t>FRDocumentReferenceDocument.content.attachment</t>
   </si>
   <si>
-    <t>FRDocumentReferenceDocument.content.attachment.contentType</t>
-  </si>
-  <si>
-    <t>FRDocumentReferenceDocument.content.attachment.language</t>
-  </si>
-  <si>
-    <t>FRDocumentReferenceDocument.content.attachment.data</t>
-  </si>
-  <si>
-    <t>FRDocumentReferenceDocument.content.attachment.url</t>
+    <t>DocumentReference.content.attachment.contentType</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.language</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.data</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.url</t>
   </si>
   <si>
     <t>FRLMAttachment.size</t>
   </si>
   <si>
-    <t>FRDocumentReferenceDocument.content.attachment.size</t>
-  </si>
-  <si>
-    <t>FRDocumentReferenceDocument.content.attachment.title</t>
+    <t>DocumentReference.content.attachment.size</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.title</t>
   </si>
 </sst>
 </file>
@@ -469,63 +475,65 @@
       <c r="D3" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" t="s" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
@@ -572,7 +580,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -587,85 +595,87 @@
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E9" s="2"/>
     </row>

--- a/main/ig/FRAttachmentLMCDAFHIR.xlsx
+++ b/main/ig/FRAttachmentLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
